--- a/data/mmendez.xlsx
+++ b/data/mmendez.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{A60841FB-322F-4DCB-8077-1F001FBBC3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDE85FD8-0702-4790-A5CB-E5B11DEB848E}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{A60841FB-322F-4DCB-8077-1F001FBBC3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0156BFF7-C32F-4D36-A08B-00DC080A622E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{F5A6AEDC-28BE-4B8A-B241-C617D1926264}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F98D0592-FCAA-4504-8375-2BF5706E5F67}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="12" bestFit="1" customWidth="1"/>
@@ -3299,35 +3299,219 @@
         <v>15</v>
       </c>
       <c r="D61" s="6">
-        <f t="shared" ref="D61" si="83">+D60+K60+E61-F61</f>
+        <f t="shared" ref="D61:D65" si="83">+D60+K60+E61-F61</f>
         <v>8970.9</v>
+      </c>
+      <c r="G61" s="6">
+        <v>125.59</v>
       </c>
       <c r="H61" s="7">
         <f t="shared" si="76"/>
-        <v>16301</v>
+        <v>16426.59</v>
       </c>
       <c r="I61" s="7">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>12.559000000000001</v>
       </c>
       <c r="J61" s="7">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>12.559000000000001</v>
       </c>
       <c r="K61" s="7">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>113.03100000000001</v>
       </c>
       <c r="L61" s="7">
         <f t="shared" si="80"/>
-        <v>14670.900000000007</v>
+        <v>14783.931000000008</v>
       </c>
       <c r="M61" s="7">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>3.7677</v>
       </c>
       <c r="N61" s="4">
         <f t="shared" si="82"/>
+        <v>1.3999710174007068E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
+        <v>45902</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="6">
+        <f t="shared" si="83"/>
+        <v>9083.9310000000005</v>
+      </c>
+      <c r="G62" s="6">
+        <v>208.93</v>
+      </c>
+      <c r="H62" s="7">
+        <f t="shared" ref="H62:H65" si="84">+H61+G62</f>
+        <v>16635.52</v>
+      </c>
+      <c r="I62" s="7">
+        <f t="shared" ref="I62:I65" si="85">+G62*0.1</f>
+        <v>20.893000000000001</v>
+      </c>
+      <c r="J62" s="7">
+        <f t="shared" ref="J62:J65" si="86">+I62</f>
+        <v>20.893000000000001</v>
+      </c>
+      <c r="K62" s="7">
+        <f t="shared" ref="K62:K65" si="87">+G62-I62</f>
+        <v>188.03700000000001</v>
+      </c>
+      <c r="L62" s="7">
+        <f t="shared" ref="L62:L65" si="88">+L61+K62</f>
+        <v>14971.968000000008</v>
+      </c>
+      <c r="M62" s="7">
+        <f t="shared" ref="M62:M65" si="89">+K62/30</f>
+        <v>6.2679</v>
+      </c>
+      <c r="N62" s="4">
+        <f t="shared" ref="N62:N65" si="90">+G62/D62</f>
+        <v>2.2999954535101598E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <v>45932</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="6">
+        <f t="shared" si="83"/>
+        <v>9271.9680000000008</v>
+      </c>
+      <c r="G63" s="6">
+        <v>194.71</v>
+      </c>
+      <c r="H63" s="7">
+        <f t="shared" si="84"/>
+        <v>16830.23</v>
+      </c>
+      <c r="I63" s="7">
+        <f t="shared" si="85"/>
+        <v>19.471000000000004</v>
+      </c>
+      <c r="J63" s="7">
+        <f t="shared" si="86"/>
+        <v>19.471000000000004</v>
+      </c>
+      <c r="K63" s="7">
+        <f t="shared" si="87"/>
+        <v>175.239</v>
+      </c>
+      <c r="L63" s="7">
+        <f t="shared" si="88"/>
+        <v>15147.207000000008</v>
+      </c>
+      <c r="M63" s="7">
+        <f t="shared" si="89"/>
+        <v>5.8413000000000004</v>
+      </c>
+      <c r="N63" s="4">
+        <f t="shared" si="90"/>
+        <v>2.0999856772585927E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>45963</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="6">
+        <f t="shared" si="83"/>
+        <v>9447.2070000000003</v>
+      </c>
+      <c r="G64" s="6">
+        <v>340.1</v>
+      </c>
+      <c r="H64" s="7">
+        <f t="shared" si="84"/>
+        <v>17170.329999999998</v>
+      </c>
+      <c r="I64" s="7">
+        <f t="shared" si="85"/>
+        <v>34.010000000000005</v>
+      </c>
+      <c r="J64" s="7">
+        <f t="shared" si="86"/>
+        <v>34.010000000000005</v>
+      </c>
+      <c r="K64" s="7">
+        <f t="shared" si="87"/>
+        <v>306.09000000000003</v>
+      </c>
+      <c r="L64" s="7">
+        <f t="shared" si="88"/>
+        <v>15453.297000000008</v>
+      </c>
+      <c r="M64" s="7">
+        <f t="shared" si="89"/>
+        <v>10.203000000000001</v>
+      </c>
+      <c r="N64" s="4">
+        <f t="shared" si="90"/>
+        <v>3.6000058006562155E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>45993</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="6">
+        <f t="shared" si="83"/>
+        <v>9753.2970000000005</v>
+      </c>
+      <c r="H65" s="7">
+        <f t="shared" si="84"/>
+        <v>17170.329999999998</v>
+      </c>
+      <c r="I65" s="7">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="7">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="7">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="L65" s="7">
+        <f t="shared" si="88"/>
+        <v>15453.297000000008</v>
+      </c>
+      <c r="M65" s="7">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="N65" s="4">
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
     </row>

--- a/data/mmendez.xlsx
+++ b/data/mmendez.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA20A423-D5DC-47BC-A943-B5EE0F492FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{BDFB3262-1312-4DD3-AEA3-C5B4FFB29A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71033D71-BB1A-4384-92DE-F61E14E1B368}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{F5A6AEDC-28BE-4B8A-B241-C617D1926264}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F98D0592-FCAA-4504-8375-2BF5706E5F67}">
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="12" bestFit="1" customWidth="1"/>
@@ -3536,7 +3536,7 @@
         <v>154.88</v>
       </c>
       <c r="H66" s="7">
-        <f t="shared" ref="H66:H69" si="92">+H65+G66</f>
+        <f t="shared" ref="H66:H68" si="92">+H65+G66</f>
         <v>17609.439999999999</v>
       </c>
       <c r="I66" s="7">
@@ -3552,7 +3552,7 @@
         <v>139.392</v>
       </c>
       <c r="L66" s="7">
-        <f t="shared" ref="L66:L69" si="96">+L65+K66</f>
+        <f t="shared" ref="L66:L68" si="96">+L65+K66</f>
         <v>15848.496000000008</v>
       </c>
       <c r="M66" s="7">
@@ -3624,43 +3624,175 @@
         <f t="shared" si="91"/>
         <v>10248.306</v>
       </c>
+      <c r="G68" s="6">
+        <v>131.56</v>
+      </c>
       <c r="H68" s="7">
         <f t="shared" si="92"/>
-        <v>17720.34</v>
+        <v>17851.900000000001</v>
       </c>
       <c r="I68" s="7">
         <f t="shared" si="93"/>
-        <v>0</v>
+        <v>13.156000000000001</v>
       </c>
       <c r="J68" s="7">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>13.156000000000001</v>
       </c>
       <c r="K68" s="7">
         <f t="shared" si="95"/>
-        <v>0</v>
+        <v>118.404</v>
       </c>
       <c r="L68" s="7">
         <f t="shared" si="96"/>
-        <v>15948.306000000008</v>
+        <v>16066.710000000008</v>
       </c>
       <c r="M68" s="7">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>3.9468000000000001</v>
       </c>
       <c r="N68" s="4">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>1.2837243540542212E-2</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
-      <c r="N69" s="4"/>
+      <c r="A69" s="3">
+        <v>46114</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="6">
+        <f t="shared" ref="D69:D70" si="99">+D68+K68+E69-F69</f>
+        <v>10366.710000000001</v>
+      </c>
+      <c r="G69" s="6">
+        <v>70.03</v>
+      </c>
+      <c r="H69" s="7">
+        <f t="shared" ref="H69:H71" si="100">+H68+G69</f>
+        <v>17921.93</v>
+      </c>
+      <c r="I69" s="7">
+        <f t="shared" ref="I69:I71" si="101">+G69*0.1</f>
+        <v>7.0030000000000001</v>
+      </c>
+      <c r="J69" s="7">
+        <f t="shared" ref="J69:J71" si="102">+I69</f>
+        <v>7.0030000000000001</v>
+      </c>
+      <c r="K69" s="7">
+        <f t="shared" ref="K69:K71" si="103">+G69-I69</f>
+        <v>63.027000000000001</v>
+      </c>
+      <c r="L69" s="7">
+        <f t="shared" ref="L69:L71" si="104">+L68+K69</f>
+        <v>16129.737000000008</v>
+      </c>
+      <c r="M69" s="7">
+        <f t="shared" ref="M69:M71" si="105">+K69/30</f>
+        <v>2.1009000000000002</v>
+      </c>
+      <c r="N69" s="4">
+        <f t="shared" ref="N69:N71" si="106">+G69/D69</f>
+        <v>6.7552772287447025E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="6">
+        <f t="shared" si="99"/>
+        <v>10429.737000000001</v>
+      </c>
+      <c r="G70" s="6">
+        <v>247.99</v>
+      </c>
+      <c r="H70" s="7">
+        <f t="shared" si="100"/>
+        <v>18169.920000000002</v>
+      </c>
+      <c r="I70" s="7">
+        <f t="shared" si="101"/>
+        <v>24.799000000000003</v>
+      </c>
+      <c r="J70" s="7">
+        <f t="shared" si="102"/>
+        <v>24.799000000000003</v>
+      </c>
+      <c r="K70" s="7">
+        <f t="shared" si="103"/>
+        <v>223.191</v>
+      </c>
+      <c r="L70" s="7">
+        <f t="shared" si="104"/>
+        <v>16352.928000000009</v>
+      </c>
+      <c r="M70" s="7">
+        <f t="shared" si="105"/>
+        <v>7.4397000000000002</v>
+      </c>
+      <c r="N70" s="4">
+        <f t="shared" si="106"/>
+        <v>2.3777205503839646E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="6">
+        <f t="shared" ref="D71" si="107">+D70+K70+E71-F71</f>
+        <v>10652.928000000002</v>
+      </c>
+      <c r="G71" s="6">
+        <v>194.22</v>
+      </c>
+      <c r="H71" s="7">
+        <f t="shared" si="100"/>
+        <v>18364.140000000003</v>
+      </c>
+      <c r="I71" s="7">
+        <f t="shared" si="101"/>
+        <v>19.422000000000001</v>
+      </c>
+      <c r="J71" s="7">
+        <f t="shared" si="102"/>
+        <v>19.422000000000001</v>
+      </c>
+      <c r="K71" s="7">
+        <f t="shared" si="103"/>
+        <v>174.798</v>
+      </c>
+      <c r="L71" s="7">
+        <f t="shared" si="104"/>
+        <v>16527.72600000001</v>
+      </c>
+      <c r="M71" s="7">
+        <f t="shared" si="105"/>
+        <v>5.8266</v>
+      </c>
+      <c r="N71" s="4">
+        <f t="shared" si="106"/>
+        <v>1.8231607310215555E-2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
